--- a/数据导出/triggers.xlsx
+++ b/数据导出/triggers.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1032,6 +1032,440 @@
         <v>46141.75373494258</v>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>62</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Configured max number of open filedescriptors is too low (&lt; {$KERNEL.MAXFILES.MIN})</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>{last()}&lt;{$KERNEL.MAXFILES.MIN}</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>91001</t>
+        </is>
+      </c>
+      <c r="H19" s="1" t="n">
+        <v>46261.35537078948</v>
+      </c>
+      <c r="I19" s="1" t="n">
+        <v>46261.35537078948</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>63</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>node_exporter is not available (or no data for 30m)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>{nodata(30m)}=1</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>2</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Failed to fetch system metrics from node_exporter in time.</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>91001</t>
+        </is>
+      </c>
+      <c r="H20" s="1" t="n">
+        <v>46261.35537078948</v>
+      </c>
+      <c r="I20" s="1" t="n">
+        <v>46261.35537078948</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>64</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>High CPU utilization (over {$CPU.UTIL.CRIT}% for 5m)</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>{min(5m)}&gt;{$CPU.UTIL.CRIT}</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>2</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>CPU utilization is too high. The system might be slow to respond.</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>91001</t>
+        </is>
+      </c>
+      <c r="H21" s="1" t="n">
+        <v>46261.35537078948</v>
+      </c>
+      <c r="I21" s="1" t="n">
+        <v>46261.35537078948</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>65</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>System time is out of sync (diff with Zabbix server &gt; {$SYSTEM.FUZZYTIME.MAX}s)</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>{fuzzytime({$SYSTEM.FUZZYTIME.MAX})}=0</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>2</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>The host system time is different from the Zabbix server time.</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>91001</t>
+        </is>
+      </c>
+      <c r="H22" s="1" t="n">
+        <v>46261.35537078948</v>
+      </c>
+      <c r="I22" s="1" t="n">
+        <v>46261.35537078948</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>66</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>System name has changed (new name: {ITEM.VALUE})</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>{diff()}=1 and {strlen()}&gt;0</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>System name has changed. Ack to close.</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>91001</t>
+        </is>
+      </c>
+      <c r="H23" s="1" t="n">
+        <v>46261.35537078948</v>
+      </c>
+      <c r="I23" s="1" t="n">
+        <v>46261.35537078948</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>67</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Operating system description has changed</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>{diff()}=1 and {strlen()}&gt;0</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Operating system description has changed. Possible reasons that system has been updated or replaced. Ack to close.</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>91001</t>
+        </is>
+      </c>
+      <c r="H24" s="1" t="n">
+        <v>46261.35537078948</v>
+      </c>
+      <c r="I24" s="1" t="n">
+        <v>46261.35537078948</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>68</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>{HOST.NAME} has been restarted (uptime &lt; 10m)</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>{last()}&lt;10m</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>2</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>The device uptime is less than 10 minutes</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>91001</t>
+        </is>
+      </c>
+      <c r="H25" s="1" t="n">
+        <v>46261.35537078948</v>
+      </c>
+      <c r="I25" s="1" t="n">
+        <v>46261.35537078948</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>69</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>High memory utilization (&gt;{$MEMORY.UTIL.MAX}% for 5m)</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>{min(5m)}&gt;{$MEMORY.UTIL.MAX}</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>3</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>The system is running out of free memory.</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>91001</t>
+        </is>
+      </c>
+      <c r="H26" s="1" t="n">
+        <v>46261.35537078948</v>
+      </c>
+      <c r="I26" s="1" t="n">
+        <v>46261.35537078948</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>70</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>High swap space usage (less than {$SWAP.PFREE.MIN.WARN}% free)</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>{Template OS Linux by Prom:system.swap.pfree[node_exporter].max(5m)}&lt;{$SWAP.PFREE.MIN.WARN} and {Template OS Linux by Prom:system.swap.total[node_exporter].last()}&gt;0</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>2</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>This trigger is ignored, if there is no swap configured.</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>91001</t>
+        </is>
+      </c>
+      <c r="H27" s="1" t="n">
+        <v>46261.35537078948</v>
+      </c>
+      <c r="I27" s="1" t="n">
+        <v>46261.35537078948</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>71</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Lack of available memory (&lt;{$MEMORY.AVAILABLE.MIN} of {ITEM.VALUE2})</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>{Template OS Linux by Prom:vm.memory.available[node_exporter].max(5m)}&lt;{$MEMORY.AVAILABLE.MIN} and {Template OS Linux by Prom:vm.memory.total[node_exporter].last()}&gt;0</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>3</v>
+      </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>91001</t>
+        </is>
+      </c>
+      <c r="H28" s="1" t="n">
+        <v>46261.35537078948</v>
+      </c>
+      <c r="I28" s="1" t="n">
+        <v>46261.35537078948</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>72</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Load average is too high (per CPU load over {$LOAD_AVG_PER_CPU.MAX.WARN} for 5m)</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>{Template OS Linux by Prom:system.cpu.load.avg1[node_exporter].min(5m)}/{Template OS Linux by Prom:system.cpu.num[node_exporter].last()}&gt;{$LOAD_AVG_PER_CPU.MAX.WARN}
+and {Template OS Linux by Prom:system.cpu.load.avg5[node_exporter].last()}&gt;0
+and {Template OS Linux by Prom:system.cpu.load.avg15[node_exporter].last()}&gt;0</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>3</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Per CPU load average is too high. Your system may be slow to respond.</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>91001</t>
+        </is>
+      </c>
+      <c r="H29" s="1" t="n">
+        <v>46261.35537078948</v>
+      </c>
+      <c r="I29" s="1" t="n">
+        <v>46261.35537078948</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>73</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Running out of file descriptors (less than &lt; 20% free)</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>{Template OS Linux by Prom:fd.open[node_exporter].last()}/{Template OS Linux by Prom:kernel.maxfiles[node_exporter].last()}*100&gt;80</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>2</v>
+      </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>91001</t>
+        </is>
+      </c>
+      <c r="H30" s="1" t="n">
+        <v>46261.35537078948</v>
+      </c>
+      <c r="I30" s="1" t="n">
+        <v>46261.35537078948</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
